--- a/WorkspaceClone_Tracking.xlsx
+++ b/WorkspaceClone_Tracking.xlsx
@@ -835,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3661,6 +3661,382 @@
       <c r="I60" t="inlineStr">
         <is>
           <t>tracker,data-integrity,not-fixed,honest-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LOG-064</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:30</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MILESTONE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>End to End</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>FEAT-070,FEAT-073</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>First live two-machine discovery: the Mac sees the Windows laptop over mDNS and can open a TCP connection to its transfer port.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>The app was built, installed to /Applications and launched. It bound TCP 50228 (not the DEFAULT_PORT 47890 - it falls back to an ephemeral port and advertises the real one, which is sensible). mDNS resolution then showed the laptop as BISWAJITA._workspace-clone._tcp.local. at 192.168.31.24:57304, advertising app_version=0.1.0, os=windows, a device_id and a static_key. A TCP connect to that port succeeded in 0.01s, so the macOS firewall is not blocking it. The presence of a device_id and static_key proves the Windows Credential Manager path works end to end: those values can only exist if the laptop read its Noise key from the keyring. The name 'BISWAJITA' confirms the BUG-018 fix. Still unproven: the Noise handshake, completing the pairing ceremony, and an actual capture-transfer-restore.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>milestone,mDNS,discovery,windows,first-live-test</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LOG-065</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Build / Release</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>FEAT-073</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Re-signed the installed .app ad-hoc; the bundled copy had an invalid resource seal.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>tauri build linker-signed the Mach-O but emitted no Contents/_CodeSignature, so spctl reported 'code has no resources but signature indicates they must be present' - the signature users see as 'the app is damaged'. Fixed on the installed copy with codesign --force --sign -. Logged as BUG-023 and deliberately NOT marked fixed at source, because every future build on a machine with no signing identity will reproduce it.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>codesign,gatekeeper,dmg,not-fixed-at-source</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>LOG-066</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:30</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Process / Tracker</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>FEAT-070</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Four verification claims from last round were false within hours; corrected.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>BUG-018..021 all said 'by inspection only' and 'the Windows build has not compiled'. The user then built and installed on Windows, and the machines discovered each other, so those lines were wrong. Corrected per-row rather than deleted, keeping the original reasoning and appending the evidence. The lesson from FEAT-067 (Done claimed for unverified work) applies in both directions: a 'not verified' claim is also a claim, and it decays just as fast. FEAT-071 was checked at the same time and correctly left In Progress - the CI workflow still has never run, and a working Windows build does not make an unexecuted workflow verified.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>corrections,tracker-honesty,verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>LOG-067</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:30</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Build / Release</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>FEAT-073</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>The app's executable inside the bundle is named 'app', which is visible in Activity Monitor and Force Quit.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>CFBundleExecutable is 'app' because the Cargo package is called app, while CFBundleName and the .app filename are 'Workspace Clone'. Users see the right name in the Dock and menu bar, but 'app' in Activity Monitor, Force Quit and in a crash report. Cosmetic, not fixed - renaming the package would touch the whole workspace and the Tauri config paths.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>cosmetic,naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LOG-068</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:45</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Devices / Pairing</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>FEAT-074</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>First live pairing attempt: nothing appeared on the Windows machine. Not a defect - the ceremony is two-sided and only one half was performed.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>The Mac showed BISWAJITA, was clicked, and displayed a 45-digit number. The Windows app displayed nothing. The cause is DEC-013: pairing is not a handshake that completes once. Each machine keeps its own trust list, so the Windows side shows a number only once someone starts a pairing from that side and selects the Mac. The user's reading - 'it should have shown up there' - is a reasonable expectation and the UI did nothing to disabuse it: the safety step said 'read it to the person at the other device' without saying that the other device has to initiate too. The dialog now spells out the other machine's three steps. Worth recording that the underlying protocol was correct and only the instruction was missing; the alternative fix, making the Windows side push a number unprompted, would have meant auto-approaching a device that had not agreed to anything.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>pairing,two-sided-ceremony,ux,first-live-test</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>LOG-069</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:45</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Devices / Pairing</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>FEAT-074</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Removed the 45-digit transcription from pairing; kept the comparison, kept the mismatch refusal.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>The user asked for the code to show on both devices and for validation to happen over the network. Accepted the first part, refused the second, and the split is the substance of this entry. The old UI asserted 'typing it is the point' and the old Rust doc asserted the field was required, both on the grounds that an uncompared number proves nothing. That justification does not hold: a caller able to invoke verify_pairing can equally pass the number the app displayed, so transcription never distinguished a human who compared from a caller who did not. It only guaranteed that a correct pairing could fail on one mistyped digit. Network validation is worse than useless: a man-in-the-middle answers both sides with its own key, both sides then agree, and the check passes while the attacker owns every transfer. The out-of-band human comparison is the control, and the recomputation from the key is what makes it meaningful. Six Rust tests cover the new rule, including that a wrong number is still refused. Renaming the parameter to confirmed_safety_number also resolved a pre-existing mismatch where the doc comment had used that name for a parameter called expected_safety_number - a divergence that would have failed at runtime, since Tauri rejects undeclared arguments, while every type check passed.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>pairing,security,safety-number,weakening-accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>LOG-070</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:45</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Process / Docs</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>FEAT-074</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>The guide contradicted the UI on which machine's name the pairing field wants, in the middle of the step the user was reading.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>The guide's ceremony step 3 said to type a name for 'the other machine' while the dialog labels the same field 'This device's name' and explains it is what the other person will see. Both readings are plausible, they are opposites, and the user met the discrepancy at exactly the moment they were trying to complete a live pairing. Fixed to match the UI. The wider point: docs written before a flow is exercised tend to describe the flow the author imagined, and this section had been written before anyone had run it against a second physical machine.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>docs,doc-ui-mismatch,first-live-test</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>LOG-071</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:50</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Build / Release</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>FEAT-073</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Fixed the bundle-signature defect at source: Tauri now ad-hoc signs, so no manual codesign step is needed per build.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>BUG-023 was logged as 'fixed' but explicitly not at source, with a note that the manual `codesign --force --sign -` would have to be repeated for every build. That was avoidable. Tauri v2 honours bundle.macOS.signingIdentity, and the value "-" means ad-hoc. With it set, a clean build logs 'replacing existing signature', emits Contents/_CodeSignature/CodeResources, and passes `codesign -v` with nothing done by hand. The symptom that motivated BUG-023 is gone: spctl reports only the expected 'rejected' for an ad-hoc unnotarized app, not 'code has no resources but signature indicates they must be present'. Recorded because the general lesson is the useful part - a manual workaround recorded as 'known limitation' is very often a config option that was never found, and the workaround hides the search.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>codesign,tauri-config,root-cause,bug-023</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9477,6 +9853,165 @@
       <c r="P73" t="inlineStr">
         <is>
           <t>Found only because CI needed it. The databases matter independently: they hold the user's own manifests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FEAT-073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>EPIC-010</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>macOS release build, DMG, and local install</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Produced a native arm64 release build and a DMG, installed the app to /Applications, and got it running with a live transfer listener. Included fixing the bundle signature (BUG-023) and confirming the first successful cross-machine discovery.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Build / Release</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:30</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>DMG at src-tauri/target/release/bundle/dmg/, app installed to /Applications, process running, TCP listener bound, zero errors in the app log.</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>All met. One caveat carried in BUG-023: the DMG on disk predates the signature fix, so it should be rebuilt before being shared anywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FEAT-074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EPIC-004</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Pairing confirmation without retyping the safety number</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Replaced the 45-digit transcription step with a visual comparison: both screens show the number, the user confirms with one button. The screen now also spells out the half the user has to perform on the *other* machine, which is the step that was actually missing during the first live pairing attempt.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Devices / Pairing</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:45</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>FEAT-013</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>No text input in the pairing dialog; both screens display the number; one button completes pairing; a supplied-but-wrong number is still refused.</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Done. The mismatch refusal was kept deliberately: the relaxation is 'no number required', not 'no number checked'. The dialog now also tells the user to start a pairing from the other machine, which is what the first live attempt was missing - that was read as a missing feature rather than a two-sided ceremony, so the instruction is now on screen instead of only in the guide.</t>
         </is>
       </c>
     </row>
@@ -13971,7 +14506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15622,7 +16157,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Partially. 7 new unit tests cover the selection logic including the Windows case, whitespace handling, and the fallback. The Windows *build* has not compiled, so the branch is exercised only as a pure function.</t>
+          <t>Yes, on a real machine. The Windows laptop advertises itself as 'BISWAJITA' in its mDNS record, which is COMPUTERNAME. Before the fix it would have announced 'This Mac'. The 7 unit tests cover the selection logic; this line is the field evidence that the fix reaches the wire.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -15642,7 +16177,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Caught by reading the platform branches for a different reason. Would have been reported by the user within one minute of installing on the laptop.</t>
+          <t>Was written as 'by inspection only'. Now confirmed: the device name on the laptop is its real computer name. Corrected 2026-09-28 after the first live two-machine discovery.</t>
         </is>
       </c>
     </row>
@@ -15709,7 +16244,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>No. By inspection only. The Windows branch cannot even be compiled here - it needs the MSVC toolchain, and cargo-xwin could not reach aka.ms to fetch the SDK.</t>
+          <t>Still partial. The Windows branch now compiles and the build completes, so the earlier 'cannot even be compiled here' caveat is gone. But the probe's result is unverified until a capture is actually run on the laptop - a build that succeeds says nothing about whether Path::exists() finds the per-user VS Code path.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -15729,7 +16264,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>The most instructive of the five: a probe that reports absence is a probe that can lie, and this one lied in the exact direction that misleads the user.</t>
+          <t>The claim to test is still the one that matters: capture on the laptop and check whether the manifest reports its editor as present.</t>
         </is>
       </c>
     </row>
@@ -15796,7 +16331,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>No. By inspection only; same uncompiled-branch caveat as BUG-019.</t>
+          <t>Partially. The laptop's mDNS record carries os=windows, so the branch compiles and runs. Whether the os_version() field itself reads a build number rather than the bare string is not yet observable from here - the TXT record uses a different, lowercase field.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -15816,7 +16351,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Fixed in both copies. They had drifted apart, which is itself the finding: the adapters version honours a WINDOWSCLONE_OS_VERSION_OVERRIDE test hook that the commands version does not.</t>
+          <t>Two separate fields both claim to be the OS name. The mDNS TXT 'os' is a lowercase slug and is not the same value as os_version(); worth reconciling so a manifest and a discovery record agree.</t>
         </is>
       </c>
     </row>
@@ -15883,7 +16418,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>No. By inspection only.</t>
+          <t>No. Edge detection is only exercised by a capture on the laptop. The build success is not evidence about it.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -15903,7 +16438,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Low impact, but it is the same failure class as BUG-019: a probe reporting absence it cannot justify.</t>
+          <t>Unchanged in substance: still waiting on a capture on Windows.</t>
         </is>
       </c>
     </row>
@@ -15981,6 +16516,93 @@
       <c r="Q23" t="inlineStr">
         <is>
           <t>Consequence for anyone using the tracker: a dependency chain read off this sheet can be silently wrong, so do not plan work from the Tasks graph until this is repaired. Needs a decision on the intended numbering, not a cleverer script.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BUG-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FEAT-073</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bundled .app had no bundle-level signature, so its resource seal was invalid</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`npx tauri build` produced a .app whose Mach-O was linker-signed (ad-hoc) but which had no Contents/_CodeSignature directory at all. The binary's own CodeDirectory claimed resources were sealed, while the bundle carried no resource envelope to match, so `spctl -a -vvv` reported 'code has no resources but signature indicates they must be present'.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Build with `npx tauri build` on a machine with no code signing identity, then run spctl -a -vvv on the resulting .app.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>A bundle whose resource seal is internally consistent.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>A broken seal, and the failure mode users report as 'the app is damaged and cannot be opened'.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No signing identity is configured on this machine (0 valid identities), and the bundler did not fall back to sealing the bundle ad-hoc even though it had no choice but to leave it unsigned.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Fixed at source by setting `bundle.macOS.signingIdentity` to `"-"` in src-tauri/app/tauri.conf.json, which tells Tauri to ad-hoc sign. The bundler now emits Contents/_CodeSignature/CodeResources on its own and logs 'replacing existing signature'; `codesign -v` passes on a freshly built bundle with no manual step. The earlier `codesign --force --sign -` on the installed copy was the manual workaround and is no longer needed.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Yes, and this time at source rather than by hand. After adding the config, a clean `tauri build` produced a bundle whose _CodeSignature exists and whose `codesign -v` passes, with no manual codesign step. The original symptom is gone: spctl no longer reports 'code has no resources but signature indicates they must be present', only the expected 'rejected', which is the distribution verdict for an ad-hoc signed unnotarized app and does not affect local launch.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:30</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Was written as 'not yet fixed at source - the DMG predates the fix'. Both statements were superseded within the hour by the signingIdentity change, and the DMG has been rebuilt since. Corrected 2026-09-28. What remains true: this is ad-hoc signing, so a DMG copied to a different Mac is still quarantined by Gatekeeper and needs right-click -&gt; Open. Ad-hoc signing cannot fix that; only notarisation would.</t>
         </is>
       </c>
     </row>
@@ -18969,7 +19591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20585,6 +21207,130 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DEC-027</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ad-hoc re-sign the installed .app rather than require a Developer ID</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>The bundled app had an invalid resource seal and no signing identity is available on this machine (0 valid identities). A Developer ID certificate would cost an Apple membership and is the wrong ask for a local test.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Leave unsigned and hope; require a Developer ID; ad-hoc seal the bundle; distribute via testflight-style signing.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ad-hoc seal the installed bundle with codesign --force --sign -.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ad-hoc signing makes the seal internally consistent, which is what Gatekeeper checks before it will load a bundle. The remaining `spctl: rejected` is the distribution verdict for an unnotarized app and does not affect local launch, because there is no quarantine attribute on something built on this machine. Escalating to a Developer ID for a first live test would be a decision about distribution that is not ready to be made.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>The app runs. Originally this decision was recorded as leaving BUG-023 open at source, because the fix was a manual per-build `codesign` step. That is superseded: `bundle.macOS.signingIdentity` is now set to "-" in tauri.conf.json, so Tauri ad-hoc signs every build and the manual step is gone. The un-solved part of the original problem is unchanged and is the part that actually matters for distribution - an ad-hoc signed, unnotarized app that is copied to another Mac is quarantined by Gatekeeper and needs right-click -&gt; Open, because there is no trusted signature to attest to. Only a Developer ID plus notarisation fixes that, and it remains the right next step when this is distributed beyond the developer's own machines.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>When the app is distributed beyond the developer's own machines, this becomes a real signing decision and needs revisiting.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>BUG-023,FEAT-073</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DEC-028</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Safety numbers are compared visually, not transcribed; the comparison stays out of band</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>The user paired for the first time across two machines and asked to drop the input, proposing that validation happen over the network once both sides show the same code. The existing code required the number to be retyped and justified that as the security control.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Keep the transcription; drop it and auto-validate over the network; drop the transcription and keep an out-of-band human comparison.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Drop the transcription, keep the comparison human and out of band, and keep refusing a supplied number that disagrees with the recomputed one.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Network validation fails against the attack it exists to prevent: a man-in-the-middle substitutes its own key, answers both sides, and both sides compute a matching number, so the check passes while the attacker controls the channel. Any check that travels the same path as the data cannot detect interception of that path. The transcription, meanwhile, was never a control - a caller that can reach the command can also pass the displayed number - so it was pure cost: 45 digits, and a correct pairing lost to a single mistyped digit. What is left is the part that genuinely works. The human compares two screens over a channel the attacker does not control, and the backend recomputes the number from the key so the paired key is provably the key that was on screen. This also matches Signal, WhatsApp and Bluetooth, which all show a number and ask for a click.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>This is a real weakening and is not claimed otherwise. Removing 45 keystrokes removes some friction, and friction is a weak way of forcing attention - a user who does not actually read the number can now click through without touching a key, where before the typing at least made them stop. The mitigation is that the number stays large and centred on both screens and completion is a deliberate labelled click rather than a default. A stronger mitigation, not implemented, would be to require the number only when the two devices are on a network the app has reason to distrust. Anyone relying on 'you must type it' as an assurance that the other person read their screen out loud is no longer getting that assurance.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>If the UI ever grows a QR path, the scan becomes the comparison and this decision gets superseded. Also revisit if there is ever a mode that pairs without any human present, which this decision explicitly forecloses.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>FEAT-074,LOG-068,LOG-069,DEC-013</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WorkspaceClone_Tracking.xlsx
+++ b/WorkspaceClone_Tracking.xlsx
@@ -835,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4037,6 +4037,335 @@
       <c r="I68" t="inlineStr">
         <is>
           <t>codesign,tauri-config,root-cause,bug-023</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>LOG-072</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:05</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>IPC / Capture</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Live two-machine test: sending a workspace failed on a casing mismatch</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>First real capture-to-send attempt returned `missing field `file_transfer``. Both types were complete and agreed on every name; they disagreed on the convention. Serde ignores unknown keys, so all five misnamed CaptureSelection fields arrived as empty lists, and only the nested Policy's first missing field stopped the command. The error named a field the caller was also sending. Fixed at source on all eleven affected fields across four types, not just the one reported.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>bug,ipc,capture,serde,live-test</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>LOG-073</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>IPC / Capture</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>FEAT-075</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Added a cross-language contract test after confirming it fails on the broken code</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>6 tests in adapters/tests/ipc_selection_contract.rs. The central one reads the real src/types/index.ts and compares field names against what serde accepts, placing a gate in the space where the bug lived. Verified by reverting the fix and re-running: 3 tests fail, reproducing the user's exact error. An honest limit was found in the process -- the field-name comparison did not catch removal of the rename_all attribute, because it converts snake_case to camelCase first and so agreed either way. A separate test now pins the convention directly, also confirmed by revert.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>test,gate,ipc,verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>LOG-074</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:10</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Network / Discovery</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Device names no longer carry the mDNS service type</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>The laptop was listed as `BISWAJITA._workspace-clone._tcp`. The full name is `{instance}.{service}.{domain}` and only the instance label is a name. Extracted `instance_display_name` to strip the whole service suffix case-insensitively, hoisted SERVICE_TYPE so registration and parsing share one constant, and rewrote the test that had been green while the bug was live. 4 new cases; 5 total. The existing test had asserted no trailing dot and no `.local` and passed happily, checking two properties that held while missing the one that was wrong.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>bug,discovery,mdns,naming,test</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>LOG-075</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:20</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Privacy / Browser</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DEC-029</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Browser history capture is a documented guarantee, not a gap</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>The user reported that open URLs are not shown on the Mac. The browser adapter reports `history_access: "none: URLs are supplied by the user"` and the developer guide promises under 'Never read from your machine at all' that browser tabs, history, profiles and session databases are never read. The capture screen has a 'One URL per line' box. Reading history would retract a documented privacy guarantee on the most sensitive data on a machine, and is not only an adapter change: Chrome's History is SQLite, locked while the browser runs, and gated on macOS behind Full Disk Access. Not implemented. Offered a clipboard-paste shortcut as the honest alternative, which needs no new permission.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>decision,privacy,browser,scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>LOG-076</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:35</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Network / Transfer</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>FEAT-075</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Added a live probe that tells a bound port from a served one</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>network/examples/live_listener_probe.rs. The receive module's own header records a build where the listener was bound and its port advertised while nothing called accept_once -- the app looked reachable and could receive nothing, and a bound port proves nothing about being served. The probe connects, sends bytes that cannot be a valid Noise handshake, and waits for the app to close: a served loop reads and drops, an unserved one never reads. Validated in both directions -- PASS against the running app, FAIL against a deliberately unserved listener. It cannot prove a transfer succeeds end to end, which needs a paired peer and a workspace.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>test,network,transfer,verification,tooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>LOG-077</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-28 20:22</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Network / Transfer</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>FEAT-075</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>BUG-026: send failed on a device discovery could see, because the send path read a map nothing ever populated</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>send_workspace looked up its destination only in TransferService::known, which remember_device() is the only writer of -- and no command ever calls it. known stayed empty for the process's whole life, so every send died with 'No device with id ... is currently reachable' before a socket opened, on a device the UI (reading discovery's own map) showed as on-network, paired and allowed to receive. Fixed by resolving from the discovery service's map first, dropping to known when an mDNS record expires, extracted as pure resolve_destination with 4 new tests; DiscoveryService gained a cfg(test) insert_for_test. Reverted to prove the tests catch the shipped bug (2 fail). 374 Rust tests green.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>bug,transfer,discovery,resolution,live-test</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>LOG-078</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-28 20:40</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Restore / Planner</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>FEAT-040</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>BUG-027: restore nested projects under the destination root, appending the source machine's folder name</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>resolve_destinations resolved root.join(project.name) for every project. The name is the source machine's folder name (openshorts from Documents/openshorts on the Mac), so restoring to E:/workspace-clone produced E:/workspace-clone/openshorts and the report asked the user to create a folder they never named. New rule: one project per bucket lands exactly in the folder typed (name never consulted, hostile names inert); several projects per bucket nest under it via safe_child. Same-name collisions warn. Revert-verified; 377 Rust / 99 vitest green.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>bug,restore,destination,planner,live-test</t>
         </is>
       </c>
     </row>
@@ -4773,7 +5102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10012,6 +10341,82 @@
       <c r="P75" t="inlineStr">
         <is>
           <t>Done. The mismatch refusal was kept deliberately: the relaxation is 'no number required', not 'no number checked'. The dialog now also tells the user to start a pairing from the other machine, which is what the first live attempt was missing - that was read as a missing feature rather than a two-sided ceremony, so the instruction is now on screen instead of only in the guide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FEAT-075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EPIC-003</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Cross-language field-name contract for IPC payloads</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>A test that reads the real TypeScript interfaces and compares them against the names serde will accept, so a field renamed in either language fails the build instead of silently producing an empty capture.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>IPC / Capture</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>100</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:40</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Renaming or adding a field in either src/types/index.ts or the Rust IPC structs fails the test suite. Verified by reverting the fix and confirming 3 tests fail, reproducing the user's exact error text.</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Done. Added in adapters/tests/ipc_selection_contract.rs, 6 tests: the real UI payload deserializes completely; a misspelled key is refused; Policy reads camelCase and still writes snake_case; a manifest round-trips unchanged; the camelCase convention itself is pinned; and TypeScript field names are compared against serde. The gate exists because BUG-024 was invisible to every check in the build. Honest limit recorded in BUG-024: the field-name comparison alone does not catch removal of the rename_all attribute, which is why the convention has its own test. Both confirmed by revert rather than assumed.</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16603,6 +17008,354 @@
       <c r="Q24" t="inlineStr">
         <is>
           <t>Was written as 'not yet fixed at source - the DMG predates the fix'. Both statements were superseded within the hour by the signingIdentity change, and the DMG has been rebuilt since. Corrected 2026-09-28. What remains true: this is ad-hoc signing, so a DMG copied to a different Mac is still quarantined by Gatekeeper and needs right-click -&gt; Open. Ad-hoc signing cannot fix that; only notarisation would.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BUG-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FEAT-075</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sending a workspace failed: missing field `file_transfer`</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The first capture-to-send attempt between the two real machines failed with `invalid args `selection` for command `capture_workspace`: missing field `file_transfer``. The error names a field the UI was in fact sending, so fixing that one field would have produced a second error immediately after.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>On the Mac, capture a workspace and send it to the paired laptop. The command rejects the payload before the capture begins.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>The selection deserializes and the workspace transfers.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>The command was rejected before the capture began, with a message naming `file_transfer` -- a field the UI was sending, under the name it was also sending. Every misnamed list field would have arrived empty, so a capture that got past this would have silently dropped selected projects and pasted URLs while still reporting success; the URLs vanishing would have pointed at the browser adapter, four functions from the actual cause.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>The capture never started. Rust read the selection as snake_case (`include_applications`, `browser_urls`, `source_path`) and the UI wrote it as camelCase (`includeApplications`, `browserUrls`, `sourcePath`). `CaptureSelection` in adapters/src/traits.rs was the one IPC-boundary type missing `#[serde(rename_all = "camelCase")]`; that convention is applied in 9 other places, all in commands/src/. Because serde ignores unknown keys, all five misnamed fields arrived as empty lists rather than errors, and only the nested `Policy` failing on the first missing field in its declaration order stopped the command -- so the error named a field the caller was also sending.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Added `#[serde(rename_all = "camelCase", deny_unknown_fields)]` to `CaptureSelection`, `SelectedProject` and `ApprovedCommand` -- all eleven affected fields across all four types, not only the one reported. `Policy` took per-field `alias`es instead (DEC-029), because it is also the manifest's policy: a blanket rename would have fixed the input and silently rewritten the manifest wire format. `deny_unknown_fields` closes the worse half of the bug (DEC-030).</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yes, at source. Confirmed by reverting the fix and re-running the new contract test: 3 of 6 tests fail, reproducing the user's exact error text, `missing field `file_transfer``.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:40</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Three gates were green while this was live: tsc checks TypeScript against its own types, cargo test builds the struct in Rust where naming is irrelevant, and check_command_parity.py compares command *names*. The bug lived in the space between them, so FEAT-075 puts a gate there. Honest limit found while testing the new gate: the field-name comparison alone did NOT catch removal of the rename_all attribute, because it converts snake_case to camelCase first and so agreed either way. A separate test pins the convention directly. Both were confirmed by revert, not assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BUG-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FEAT-075</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Discovered devices listed with the mDNS service type glued to the name</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>The paired laptop appeared in the device list as `BISWAJITA._workspace-clone._tcp` rather than `BISWAJITA`.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Pair a device and open the Devices screen.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>The device is listed under the name its owner chose.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>The name carried `._workspace-clone._tcp`.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>`parse_discovered_device` took the mDNS full name and stripped the trailing dot and the `.local` domain, but never the service type. The comment beside that code said the goal was a name that helps a person recognise their own machine -- so the code was the bug the comment was warning about, not the one it described.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Extracted `instance_display_name`, which strips the whole service suffix (case-insensitively, since mDNS names are) rather than a `.local` substring, and hoisted the service type to a `SERVICE_TYPE` constant used by both registration and parsing so the two halves cannot drift. Substring stripping was avoided deliberately: a Mac genuinely named `ABHISHEKs-MacBook-Air.local` must keep its `.local`, or the app would rename a device to something its owner never chose.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yes, and the test that was green while the bug was live was the tell.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:10</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>`the_display_name_is_not_a_dns_name` already existed, asserted that the name has no trailing dot and no `.local`, and passed throughout. It checked two properties that happened to hold while missing the one that was wrong. It now asserts the exact expected value, plus four new cases: a display name that itself ends in `.local`, mixed-case service types, an unrecognised full name, and a degenerate one that must not reduce to empty. The last two guard the 'never lose a device to a naming quirk' rule. Confirmed the strengthened test fails on the old code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BUG-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FEAT-075</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Send failed: 'No device with id ... is currently reachable' for a device the UI showed as on-network, paired and allowed to receive</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>The first real send attempt on the Mac against the paired laptop failed before a socket was ever opened, with: Network error: Connection failed: No device with id 'hnODGDVs/oYDiOhuQO941A==' is currently reachable. Check that it is running, on the same network, and that discovery has found it on this screen. The device the message denied seeing was simultaneously listed on the very screen the user was looking at, shown as on-network, paired, and permitted to receive.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>On the Mac, with the laptop discovered (the Send button enabled), click Send workspace.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>The send starts and the transfer proceeds.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>The send failed with 'No device with id ... is currently reachable' -- the wording telling the user discovery had not found the device, when the screen it told them to check was proving the opposite.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>send_workspace resolved its destination only from TransferService::known, a second map fed exclusively by remember_device() -- a method nothing in the workspace ever calls, let alone a command. known was therefore empty for the whole lifetime of the process, so every send failed here regardless of what discovery knew. Discovery's own map, the one get_discovered_devices reads and the mDNS browse loop actually fills, was never consulted. The comment above the lookup even claimed peers are found 'in two places ... what discovery has seen on the network right now, and what a previous command recorded' -- only one lookup existed and it read the wrong map. The e2e integration test stayed green because it hands a hand-built peer record straight to TransferService::send_workspace and never exercises the command's destination resolution.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Resolve the destination from the discovery service's map first (the map the browse loop writes and get_discovered_devices reads), with TransferService::known as the fallback for a record whose mDNS entry has expired. Extracted as a pure function resolve_destination(from_discovery, remembered, device_id) per DEC-026 so the two-source rule is testable; the payload/authorization steps are unchanged and happen before the transfer lock, and the discovery lookup happens before the transfer lock so the two locks are never nested. The error message now distinguishes being unreachable from being untrusted, and no longer tells the user to verify on the screen that shows the device.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yes, at source, by revert. Restoring the shipped order (only the remembered map consulted) fails two of the four new tests: a_send_resolves_a_destination_that_only_discovery_can_see and discovery_wins_over_a_stale_remembered_record. With the fix, all 66 commands-lib tests and all 374 workspace tests pass. An earlier attempt that merely swapped the or_else order also failed the discovery_wins test -- so the order rule has teeth as well as the primary-source rule.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-09-28 20:22</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Also added DiscoveryService::insert_for_test (cfg(test) only) so a test can prove get_device reads the same map the browse loop writes. The four tests: discovery alone resolves a send (the real Field state: remembered is None), discovery beats a stale address, a remembered peer survives record expiry, and a device in neither map is refused without the self-contradicting wording.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BUG-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FEAT-040</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Restore appends the source machine's folder name to the destination the user typed</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Restoring the transferred workspace on the Windows laptop: the user typed E:/workspace-clone as the destination folder and the plan produced E:/workspace-clone/openshorts. The extra 'openshorts' is the project's manifest name, which is simply the last folder of the source path on the Mac (Documents/openshorts). The source machine's folder name was leaked onto the destination layout, where it means nothing, and the restore report then asked the user to go and create a folder they never named.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>On the receiving machine, open a restored workspace, click Restore, type E:/workspace-clone as the destination for a bucket whose single project came from ~/Documents/openshorts, and inspect the plan.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>The typed folder is the project's destination: the code lands in E:/workspace-clone, exactly as written.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>The plan step read 'openshorts maps to E:/workspace-clone/openshorts' -- the chosen root with the source folder name appended.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>resolve_destinations always resolved root.join(project.name). project.name comes from the source machine (the capture derives it from the selected folder), so a root the destination user chose was silently treated as a parent folder, and every bucket got a subfolder named after something local to the other machine. The reuse was deceptive: on the sending machine the name is the project folder (sensible), on a different machine's layout it is arbitrary. BUG-027 is the first restore-place failure seen on two real machines; the two-device tests all used synthetic names on one layout, so the leak never showed.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>resolve_destinations now counts the projects per bucket: a bucket holding exactly one project uses the chosen folder itself as that project's destination (the user's typed path is the folder the code lands in -- no append, and the manifest name is not consulted at all, which also makes a solitary bucket immune to a hostile name); a bucket holding several projects nests each beneath the chosen folder via the existing safe_child gate, so collisions are avoided and nothing can escape the chosen root. Same-name collisions in a crowded bucket now emit a warning. The plan preview copy explains the rule, and per-project steps still show the exact final path before anything runs.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yes. a_single_project_lands_exactly_in_the_folder_typed reproduces the user's exact case and fails on the old code (it asserted .../openshorts). Revert-verified: restoring root.join(name) for a solitary project fails that test plus a_solitary_project_ignores_a_hostile_name. 377 Rust tests, 99 vitest, tsc clean.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-09-28 20:40</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>User's decision (2026-09-28): exact folder for one project; nested only when a bucket holds several. Frontend copy in RestorePreviewScreen updated to state the rule. The laptop needs this fix for the restore side: planner.rs + RestorePreviewScreen.tsx must reach the Windows build.</t>
         </is>
       </c>
     </row>
@@ -19591,7 +20344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21331,6 +22084,130 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DEC-029</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Policy takes camelCase aliases rather than a camelCase rename</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`Policy` is deserialized from two places that use two different conventions: inside a `CaptureSelection` arriving over IPC, where the TypeScript is camelCase, and inside the manifest, which is snake_case on the wire by DEC-012.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Blanket `rename_all = "camelCase"` (fixes input, rewrites the wire format); rename the TypeScript to snake_case (breaks the 9-place convention); per-field `alias` (accepts both, writes one); a separate boundary type (no alias risk, two types to keep in step).</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Per-field `alias` on the three multi-word fields, so both spellings deserialize and exactly one is ever written.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>A blanket rename would have appeared to work -- the capture would succeed -- while changing the manifest format for every stored and transferred manifest, which is a compatibility break in a field nothing tests. A separate type would be cleaner in principle but means two structs to keep in step forever. The alias keeps one type, accepts both spellings, and fails loudly if both are present.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>The manifest wire format is unchanged, verified by a round-trip test. The four Policy fields are the only ones needing this treatment; `clipboard` is one word and is spelled the same in both conventions, so an alias for it would have been misleading.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>If the manifest ever gains its own versioning per field, or the IPC boundary moves off Tauri's automatic argument mapping.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>BUG-024,FEAT-075</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DEC-030</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>IP payloads deny unknown fields instead of ignoring them</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Serde ignores an unrecognised key by default, so a field the UI sends under a name the Rust struct does not know arrives as an empty list, not an error.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Leave the default (silent); reject the whole payload on an unknown key; log a warning and continue.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Reject the payload.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Silent truncation is the worst available outcome: a capture completes, reports success, and quietly omits what the user selected. The symptom points somewhere else entirely -- in BUG-024 the URLs vanished and the browser adapter looked at fault, when the cause was four functions away. A user who selects three projects and pastes two URLs cannot tell an empty list that arrived empty from one that was dropped in transit. The UI and the Rust types are hand-mirrored in two languages, so the realistic failure is a typo, and a typo should stop the capture.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>A field added in TypeScript before the Rust struct catches up now fails the command loudly instead of arriving empty. Applied to the three capture-selection types; deliberately NOT applied to `Policy`, which is also a wire format, where the manifest's own schema validation is the right mechanism and an unknown field could come from a newer sender.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>If the frontend ever needs to send fields the backend does not model, or if a version skew between machines becomes possible.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>BUG-024,FEAT-075</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WorkspaceClone_Tracking.xlsx
+++ b/WorkspaceClone_Tracking.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Phase 4 - LAN Transfer: receive path complete, verified in the running application</t>
+          <t>Phase 4 - LAN Transfer: receive path complete and workspace files travel and restore; Phase 5 (Linux, relay, team features) not started</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -715,12 +715,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 17:40</t>
+          <t>2026-09-28 21:45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>EPIC-006 corrected from Done to In Progress. Phase 5 (Linux, relay, team features) is Not Started.</t>
+          <t>Workspace files are now captured, carried and restored end to end. Windows is still implemented but unverified on the hardware; the DMG is built on the Mac.</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>348 Rust tests (11 of them two-device end-to-end across a real socket), 37 frontend tests, 0 build warnings, command-surface parity clean at 44/44</t>
+          <t>394 Rust tests (12 of them two-device end-to-end across a real socket; 13 in the new files crate), 99 frontend tests, 0 build warnings, command-surface parity clean at 44/44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-27 17:40</t>
+          <t>2026-09-28 21:45</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Up from 325/19. The two-device suite is the only layer that exercises what the app exists to do, and the two launch-path bugs in this batch (BUG-010, BUG-011) were found by running the application, not by any test.</t>
+          <t>Up from 377/99. The files crate, the wire envelope, and the restore extract path are fully covered; the two-device suite now proves a file changed on the sending machine restores with the changed content on the receiving machine.</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4366,6 +4366,382 @@
       <c r="I75" t="inlineStr">
         <is>
           <t>bug,restore,destination,planner,live-test</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>LOG-079</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:45</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Core / Files</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>FEAT-076</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Built the files crate: snapshot, archive, transit</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>New crate src-tauri/files. snapshot.rs: sorted deterministic tar built at capture time -- denylists for directories and files matched at any depth, per-file 128 MiB cap, 512 MiB total cap, symlinks skipped, every skip and the overflow surfaced. archive.rs: extraction treats every entry as hostile -- refuses traversal names, absolute paths, backslashes, drive letters, symlinks, reserved Windows device names and oversized entries, and caps the total. transit.rs: the WCFB1 envelope wrap/unwrap. 13 tests, 0 warnings.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>files,archive,snapshot,denylist,caps</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>LOG-080</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:45</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>IPC / Capture</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>FEAT-076</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Capture now snapshots, seals and stores the file archive at capture time</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>snapshot_and_store walks the selected projects, seals the tar with the storage key, writes it to files/{id}.files.sealed, and upserts the workspace_files row (migration 003). CaptureResult carries file_count and byte_count; every skip and the overflow become capture warnings. The exact same bytes are what a re-send puts on the wire.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>capture,files,snapshot,sealed</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>LOG-081</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:45</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Network / Transfer</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>FEAT-077</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>The wire now carries the archive behind the manifest, in an opaque envelope</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>transfer_payload replaced manifest_payload at the send site: WCFB1 magic, u32 LE manifest length, manifest JSON, archive -- inside the existing encrypted chunked frames, with no change to framing. The receive side splits the envelope; a payload without the magic reads back as manifest-only, so every pre-feature sender still arrives. The accept-side budget rose to 512 MiB + 32 MiB headroom, and the arrived archive is unsealed with the receiver's own key and stored exactly as a local capture stores one.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>transfer,wire,envelope,backward-compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LOG-082</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:45</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Restore / Planner</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>FEAT-079</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Restore gained an extract-files step per placed project</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>The planner adds extract-files-{proj} (required, dep map-path-{proj}); the executor receives files: Option&lt;&amp;[u8]&gt; and calls the hostile extractor per project into its mapped folder, overwriting what is there. The step message reports files written and bytes, refusals and overflow; a workspace with no files reports an honest success. 43 restore tests incl. two new extract tests; the two-device e2e asserts that a file changed on the sending machine has the changed content on the receiving machine after send + restore.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>restore,extract,planner,executor,e2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>LOG-083</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:45</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATION</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>FEAT-080</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Frontend wired for the file feature</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>extract_files joined RestoreActionType; the restore preview and report render the step with its own icon and the preview classifies it as an execution step, so the 'commands will run' warning stays honest. The capture policy defaults to 'all' -- the UI's only choice for a fresh capture is to carry files, which is the point of a clone; 'none' and 'explicit' remain in the type. The capture screen's 'What is never captured' notice states the snapshot's denylist and corrects the stale claim that working-tree files are never copied.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>frontend,restore-preview,restore-report,capture-policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>LOG-084</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:45</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RUN-024,RUN-025,RUN-026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Full gates green: 394 Rust, 99 frontend, tsc clean</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>cargo test --workspace -- --test-threads=2: 394 passed, 0 failed -- up from 377 by 17 (files crate 13, the two-device files e2e 1, restore extracts 2, one further command unit). npx vitest run: 99/99 across 6 files. npx tsc --noEmit: clean. Command-surface parity and the design-token check are clean too. No test asserted a manifest-only capture default, so defaulting the policy to 'all' stayed green.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>testing,regression,full-run</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>LOG-085</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:45</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>IMPROVEMENT</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>FEAT-045 corrected, guide and tracker aligned to the file feature</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>FEAT-045 was Done at 100% for 'file transfer' while only the manifest policy flag existed; its row now says exactly that, and the transport is FEAT-076..080. DEVELOPER_GUIDE updated: the capture section states the denylist and caps, restore step 3 documents the extract step, the wire diagram shows the envelope and the extract step, the privacy section distinguishes the adapters' promises from the file snapshot's, and the test counts are 394/99.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>correction,documentation,guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>LOG-086</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:30</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Build / Release</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RUN-028,FEAT-073</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>DMG built and verified: Workspace Clone_0.1.0_aarch64.dmg, 8.2 MB</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>npx tauri build ran the frontend build, the Rust release build (no code warnings), and bundle_dmg.sh. The only output was a tauri-build deprecation notice -- STATIC_VCRUNTIME is deprecated, use build.windows.staticVCRuntime in tauri.conf.json -- which fires in the release profile only, concerns Windows CRT linking, and originates in the tauri-build dependency rather than any crate in this workspace. Left as a documented note rather than patched blind: the config key it asks for changes the Windows installer's runtime linking, which can only be verified on the Windows laptop. The debug build gate stays warning-free.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>build,release,dmg,deferred-note</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P76"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8263,7 +8639,11 @@
           <t>Post-MVP per blueprint</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [Corrected 2026-09-28] This row stood for the manifest *policy flag* only. The real transport is FEAT-076 (snapshot), FEAT-077 (wire), FEAT-078 (storage) and FEAT-079 (restore); the UI wiring is FEAT-080. See LOG-085.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -10417,6 +10797,386 @@
       <c r="P76" t="inlineStr">
         <is>
           <t>Done. Added in adapters/tests/ipc_selection_contract.rs, 6 tests: the real UI payload deserializes completely; a misspelled key is refused; Policy reads camelCase and still writes snake_case; a manifest round-trips unchanged; the camelCase convention itself is pinned; and TypeScript field names are compared against serde. The gate exists because BUG-024 was invisible to every check in the build. Honest limit recorded in BUG-024: the field-name comparison alone does not catch removal of the rename_all attribute, which is why the convention has its own test. Both confirmed by revert rather than assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FEAT-076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EPIC-008</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>File snapshot at capture (denylist + size caps)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>At capture time every selected project's folder is walked and built into one sorted tar containing everything minus the denylist: version-control internals (.git, .svn), dependency and build output (node_modules, target, dist, build, .next, .nuxt, .output, .turbo, .parcel-cache), caches (.cache, __pycache__), virtualenvs (.venv, venv), Pods, DerivedData, coverage, plus the secret files: .env and .env.*, *.pem, *.key, id_rsa/id_ed25519/id_ecdsa/id_dsa, Thumbs.db, desktop.ini, databases (*.db/-shm/-wal, *.sqlite/*.sqlite3) and logs (*.log), all matched at any depth. Symlinks are skipped. A single file over 128 MiB is skipped with a reason; once the total reaches 512 MiB the walk stops and reports the overflow. The snapshot is the copy that will be re-sent, so re-sending is idempotent.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Core / Files</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>100</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:30</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>DEC-031</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Equal folders produce byte-identical archives (sorted entry order, no compression). Every denylisted name is excluded at any depth. An over-cap file is skipped and named. The total cap stops the walk and sets overflow. Every skip and the overflow surface as capture warnings.</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>New crate src-tauri/files. The capture screen's 'what is never captured' notice and the developer guide now state the denylist explicitly; what is excluded is regenerable build output or secrets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FEAT-077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>EPIC-006</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>File archive on the wire (opaque envelope, chunking unchanged)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>send_workspace now wraps the payload: MAGIC (WCFB1) then a u32 LE manifest length, then the manifest JSON, then the archive tar, sent inside the existing framed, acked, encrypted channel. The wire envelope is opaque to transport; nothing about chunk framing or the Noise channel changed. Payloads without the magic read back as manifest-only, so every pre-feature transfer still arrives exactly as before. The accept side's incoming budget is raised to the 512 MiB total cap plus 32 MiB of headroom.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Network / Transfer</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>100</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:30</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>DEC-032</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>A workspace with files arrives and opens with the receiver's key; a legacy manifest-only payload arrives byte-for-byte as before. The e2e suite proves both directions.</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>The receive side unseals the archive with its own key, so a received workspace is indistinguishable from a local capture. No relay or additional key exchange was introduced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FEAT-078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EPIC-006</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sealed archive storage + workspace_files table</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>The sealed archive lives at &lt;data_dir&gt;/files/{id}.files.sealed, sealed with the storage key like the manifest. Migration 003 adds the workspace_files table; the repository records the sealed path, file count, byte count and archive format. The receive path unseals the arrived archive with the receiving machine's own key and stores it the same way, and restore reads it back by workspace id through the same repository.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Tauri Commands / DB</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>100</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:30</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>DEC-032</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>A captured workspace and a received workspace are stored identically; the files restore by workspace id with no extra configuration.</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>The archive for a workspace the denylist emptied or that overflowed is still recorded, so the board and the restore report can say what a workspace carries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FEAT-079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EPIC-008</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Restore extracts project files</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>The restore planner adds a required extract-files step for every project with a destination, dependent on its map-path step and ordered before anything that inspects or opens the project. The executor hands the unsealed tar to the archive extractor, which writes each project's entries into its mapped folder overwriting what is there (the snapshot is authoritative), refuses traversal names, absolute paths, backslashes, drive letters, symlinks, reserved Windows device names and oversized entries, and caps the total. The step message reports files written, bytes, refusals and overflow; a workspace captured without files reports an honest success.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Core / Restore</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>100</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:30</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>DEC-032</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>A project's changed file restores over an existing file. Unsafe entries are refused, not followed or written. 43 restore tests incl. 2 extract tests; the two-device e2e asserts the changed file's content on the receiving machine.</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>ExtractFiles is a distinct RestoreActionType, so the preview and report render and gate it like any other step instead of it being a hidden side effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FEAT-080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EPIC-009</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>File transfer defaulted on; restore steps rendered</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>New captures default to file transfer policy 'all' -- the capture screen is the single place the decision is made, and a fresh capture that silently reverted to manifest-only would defeat the feature no matter what the screen said. The restore preview and restore report render the extract-files step with its own icon and status, and classify it as an execution step so the 'commands will run' warning stays honest. The capture screen's 'What is never captured' notice now states the file snapshot's denylist and corrects the stale claim that working-tree files are never copied.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Frontend / Screens</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>100</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:30</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>FEAT-076,FEAT-079</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>A capture built from a fresh selection carries files by default. RestoreActionType includes extract_files; preview and report render it; 'commands will run' covers it.</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>The size caps and the denylist are what keep 'all' safe; manifest-only remains available in the policy type for when per-project selection or a no-files choice is built into the UI.</t>
         </is>
       </c>
     </row>
@@ -18178,7 +18938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19724,6 +20484,302 @@
       <c r="N24" t="inlineStr">
         <is>
           <t>Logged as a run precisely so the absence is a record rather than an omission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RUN-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rust / whole workspace</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>cargo test --workspace -- --test-threads=2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:22</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>90</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>394 passed, 0 failed, 0 build warnings. Per layer: adapters 62, ipc_selection_contract 6, commands 66, two_device_transfer 12, core 16, crypto 24, db 5, files 13, network 68, loopback 8, preflight 71, restore 43. Up from 377 by 17: the files crate (13) plus the files e2e in the two-device suite (1) plus restore's two extract tests and one further command test.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>The new e2e a_workspace_with_files_arrives_with_its_archive_and_restores sends a workspace whose file was changed on the sending side, and asserts the changed content is present after receive + restore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RUN-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>npx vitest run</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:18</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:19</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6 test files, 99 passed, 0 failed.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>No test asserted a manifest-only default, so the policy default change to 'all' stayed green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RUN-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>npx tsc --noEmit</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:18</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:18</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Clean, no output, no errors.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Runs over the edited RestoreActionType union and the new screen icons/imports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RUN-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tooling gates</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>python3 scripts/check_command_parity.py &amp;&amp; python3 scripts/apply_design_tokens.py --check</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:46</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:46</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PARITY OK: every command Rust registers is called and every call resolves. No raw palette colours remain in src/.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>The full green run also needs these two, plus the DMG build (RUN-028).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RUN-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Build / Release</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>npx tauri build (frontend + Rust release + DMG)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:26</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>240</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Workspace Clone_0.1.0_aarch64.dmg, 8.2 MB, plus the .app bundle. Ad-hoc signed (signingIdentity '-'). beforeBuildCommand ran npm run build first. One deprecation warning from tauri-build about STATIC_VCRUNTIME (release-profile only, Windows CRT config, not from any crate in the workspace); see LOG-086.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>src-tauri/target/release/bundle/dmg/Workspace Clone_0.1.0_aarch64.dmg</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>The debug gate the guide mandates (cargo build --workspace) remains warning-free; the release warning is toolchain-level and logged rather than patched blind.</t>
         </is>
       </c>
     </row>
@@ -20344,7 +21400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22208,6 +23264,130 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DEC-031</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>File scope is 'everything minus junk', snapshotted at capture time</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A captured workspace must carry the actual project files, so a file changed on the Mac exists on the Windows laptop after send + restore. The manifest policy column file_transfer already existed; nothing implemented it. Two coupled choices had to be made first: what counts as 'the files', and when the copy is made.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>(a) Keep manifest-only. (b) Snapshot at capture time. (c) Snapshot at send time. Within (b), scope could be every selected project's folder wholesale, or a curated allowlist, or 'everything minus a denylist'.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>(b) with 'everything minus two denylists and two caps'. At capture time: denied directories (.git, node_modules, target, dist, build, .next, .nuxt, .output, caches, virtualenvs, Pods, DerivedData, coverage) and denied files (.env/.env.*, keys, databases, logs, *.db, *.sqlite, Thumbs.db, desktop.ini) at any depth; symlinks skipped; one file over 128 MiB skipped and named; total capped at 512 MiB. Explicit policy is treated as All with a warning, since per-project selection is not built yet.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>(c) means the copy changes between capture and send, so re-sending would re-send a different workspace -- the one property a re-send must not have. An allowlist is unmaintainable and would miss real projects; 'everything minus junk' is safe precisely because every excluded name is either regenerable build output or a secret. The caps keep the payload honest against the wire and the receiver's budget; the denylist keeps 'everything' safe.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>A 13-test files crate; capture stores a sealed tar plus counts; re-send re-sends the same copy; legacy manifest-only payloads and the policy value 'none' still work. The capture screen defaults the policy to 'all' (FEAT-080).</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Revisit when per-project file selection is wanted, which turns the Explicit policy from an alias into a real feature.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>FEAT-076,FEAT-077</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DEC-032</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The archive travels in an opaque envelope; restore runs as an ExtractFiles step</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>The wire already carries chunked, acked, encrypted opaque bytes, so carrying the archive required no change to framing or transport -- what had to change was the receive side's size budget and what the receiver does with the bytes. Storing and restoring also had two shapes available: formal storage plus a planner step, or a side file the restore command reads ad hoc.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>(a) Extend the existing manifest payload with fields. (b) Wrap payload as MAGIC + u32 LE manifest length + manifest + archive, treating anything without the magic as legacy manifest-only. (c) Side-channel the archive entirely (separate transfer, separate storage). Restore: (d) a special-cased ExtractFiles RestoreActionType planned after map-path, or (e) a hidden file copy inside restore with no step and no preview.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>(b) and (d). Envelope WCFB1 | u32 LE manifest length | manifest | archive. The receiver splits the envelope, unseals the archive with its own key, stores it at files/{id}.files.sealed, and records counts in the workspace_files table (migration 003). The planner emits extract-files-{proj} (required, dependent on map-path-{proj}); the executor takes files: Option&lt;&amp;[u8]&gt; and extracts per project into its mapped destination, overwriting existing files (snapshot authoritative). The accept-side incoming budget rises to the 512 MiB total plus 32 MiB headroom.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>(a) would deny unknown-field-free manifests and break every stored payload. (c) splits one logical transfer into two atomicity domains. (e) hides the one thing a restore does that touches the disk -- the preview and the 'commands will run' warning would lie. (b)+(d) keep the transport untouched, the received workspace indistinguishable from a local capture, the report telling the truth about refusals and overflow, and a no-files workspace reporting an honest success.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Legacy payloads read back manifest-only, so pre-feature senders still arrive. 43 restore tests incl. the two extract tests; the two-device e2e proves the changed file restores. The restore report's step message carries counts, refusals and overflow.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Revisit if compression ever becomes worthwhile: the size math the signature and the caps rely on would change.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>FEAT-077,FEAT-078,FEAT-079</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WorkspaceClone_Tracking.xlsx
+++ b/WorkspaceClone_Tracking.xlsx
@@ -835,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4742,6 +4742,53 @@
       <c r="I83" t="inlineStr">
         <is>
           <t>build,release,dmg,deferred-note</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>LOG-087</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:10</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Project Data</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>BUG-022</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tasks sheet renumbered and dependency columns fixed</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>BUG-022 fixed per the chosen option (second block renumbered): rows 42-73 became TASK-041..TASK-072 in row order, so all 72 task rows now have unique IDs (the 14 shared IDs are gone). The 67 dependency lists sitting in the Assignee column (38 first-block + 29 second-block rows) moved into the Dependencies column. References remapped by the first-occurrence rule: only labels whose first sheet occurrence is in the second block changed -- TASK-042-&gt;056, TASK-047-&gt;061, TASK-048-&gt;062, TASK-056-&gt;068; ambiguous labels TASK-031..040 resolve to the canonical first block and were left as written. Caveat: the dependency VALUES were bulk-populated when the sheet was built and their semantics remain the original author's intent, not a derived DAG -- but the column each chain sits in is now the one its header names. Re-verified by script asserts on 2026-09-28.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>bug,data-quality,tasks-sheet,correction</t>
         </is>
       </c>
     </row>
@@ -11407,12 +11454,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>TASK-001</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
@@ -11468,12 +11515,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>TASK-002</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
@@ -11529,12 +11576,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>TASK-002</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
@@ -11590,12 +11637,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>TASK-003, TASK-004</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
@@ -11651,12 +11698,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>TASK-005</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
@@ -11712,12 +11759,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>TASK-006</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
@@ -11773,12 +11820,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>TASK-001</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
@@ -11834,12 +11881,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>TASK-008</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
@@ -11895,12 +11942,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>TASK-004</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
@@ -11956,12 +12003,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>TASK-010</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
@@ -12017,12 +12064,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>TASK-003</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
@@ -12135,12 +12182,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>TASK-013</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
@@ -12196,12 +12243,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>TASK-014</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
@@ -12257,12 +12304,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>TASK-014</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
@@ -12318,12 +12365,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>TASK-016</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
@@ -12379,12 +12426,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>TASK-001</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
@@ -12440,12 +12487,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>TASK-018</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
@@ -12501,12 +12548,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>TASK-018</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
@@ -12562,12 +12609,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>TASK-020</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
@@ -12623,12 +12670,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>TASK-018</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
@@ -12684,12 +12731,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>TASK-018</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
@@ -12745,12 +12792,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>TASK-018</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
@@ -12806,12 +12853,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>TASK-018</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
@@ -12867,12 +12914,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>TASK-018</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
@@ -12928,12 +12975,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>TASK-018</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
@@ -12989,12 +13036,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>TASK-023..027</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
@@ -13050,12 +13097,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>TASK-014</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
@@ -13111,12 +13158,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>TASK-029</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
@@ -13172,12 +13219,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>TASK-030</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
@@ -13233,12 +13280,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>TASK-030</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
@@ -13294,12 +13341,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>TASK-030</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
@@ -13355,12 +13402,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>TASK-030</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
@@ -13416,12 +13463,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>TASK-029</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
@@ -13477,12 +13524,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>TASK-029</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
@@ -13538,12 +13585,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>TASK-036</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
@@ -13599,12 +13646,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>TASK-035</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
@@ -13660,12 +13707,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>TASK-037</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
@@ -13721,12 +13768,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>TASK-033, TASK-018</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
@@ -13735,7 +13782,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TASK-031</t>
+          <t>TASK-041</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -13782,12 +13829,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>TASK-040</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
@@ -13796,7 +13843,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TASK-032</t>
+          <t>TASK-042</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -13843,12 +13890,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>TASK-040</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
@@ -13857,7 +13904,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TASK-033</t>
+          <t>TASK-043</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -13904,12 +13951,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>TASK-040</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
@@ -13918,7 +13965,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TASK-034</t>
+          <t>TASK-044</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -13965,12 +14012,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>TASK-040</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
@@ -13979,7 +14026,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TASK-034</t>
+          <t>TASK-045</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -14026,12 +14073,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>TASK-040</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
@@ -14040,7 +14087,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TASK-035</t>
+          <t>TASK-046</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -14087,12 +14134,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>TASK-040</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr"/>
@@ -14101,7 +14148,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TASK-036</t>
+          <t>TASK-047</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -14148,12 +14195,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>TASK-040</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
@@ -14162,7 +14209,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>TASK-036</t>
+          <t>TASK-048</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -14209,12 +14256,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>TASK-040</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
@@ -14223,7 +14270,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>TASK-037</t>
+          <t>TASK-049</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -14270,12 +14317,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>TASK-040</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr"/>
@@ -14284,7 +14331,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>TASK-037</t>
+          <t>TASK-050</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -14331,12 +14378,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>TASK-037</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr"/>
@@ -14345,7 +14392,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>TASK-038</t>
+          <t>TASK-051</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -14392,12 +14439,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>TASK-037</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
@@ -14406,7 +14453,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>TASK-038</t>
+          <t>TASK-052</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -14453,12 +14500,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>TASK-037</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr"/>
       <c r="P53" s="2" t="inlineStr"/>
@@ -14467,7 +14514,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TASK-039</t>
+          <t>TASK-053</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -14514,12 +14561,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>TASK-038</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr"/>
@@ -14528,7 +14575,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TASK-040</t>
+          <t>TASK-054</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -14575,12 +14622,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>TASK-038</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr"/>
       <c r="P55" s="2" t="inlineStr"/>
@@ -14589,7 +14636,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TASK-041</t>
+          <t>TASK-055</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -14636,12 +14683,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>TASK-038</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr"/>
@@ -14650,7 +14697,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>TASK-042</t>
+          <t>TASK-056</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -14697,12 +14744,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>TASK-037</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr"/>
       <c r="P57" s="2" t="inlineStr"/>
@@ -14711,7 +14758,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>TASK-043</t>
+          <t>TASK-057</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -14758,12 +14805,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>TASK-042</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>TASK-056</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr"/>
       <c r="P58" s="2" t="inlineStr"/>
@@ -14772,7 +14819,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TASK-044</t>
+          <t>TASK-058</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -14819,12 +14866,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>TASK-001</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr"/>
       <c r="P59" s="2" t="inlineStr"/>
@@ -14833,7 +14880,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TASK-045</t>
+          <t>TASK-059</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -14880,12 +14927,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>TASK-032</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="inlineStr"/>
@@ -14894,7 +14941,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>TASK-046</t>
+          <t>TASK-060</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -14941,12 +14988,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>TASK-022</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr"/>
       <c r="P61" s="2" t="inlineStr"/>
@@ -14955,7 +15002,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>TASK-047</t>
+          <t>TASK-061</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -15002,12 +15049,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="n"/>
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>TASK-028</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr"/>
@@ -15016,7 +15063,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>TASK-048</t>
+          <t>TASK-062</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -15063,12 +15110,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>TASK-039</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr"/>
       <c r="P63" s="2" t="inlineStr"/>
@@ -15077,7 +15124,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TASK-050</t>
+          <t>TASK-063</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -15124,12 +15171,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>TASK-040</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr"/>
@@ -15138,7 +15185,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TASK-052</t>
+          <t>TASK-064</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -15185,12 +15232,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>TASK-040</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr"/>
@@ -15199,7 +15246,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>TASK-053</t>
+          <t>TASK-065</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -15246,12 +15293,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>TASK-047</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="n"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>TASK-061</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="inlineStr"/>
@@ -15260,7 +15307,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TASK-054</t>
+          <t>TASK-066</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -15307,12 +15354,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>TASK-048</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>TASK-062</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr"/>
       <c r="P67" s="2" t="inlineStr"/>
@@ -15321,7 +15368,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>TASK-055</t>
+          <t>TASK-067</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -15368,12 +15415,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>TASK-001</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr"/>
@@ -15382,7 +15429,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>TASK-056</t>
+          <t>TASK-068</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -15429,12 +15476,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>TASK-014</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr"/>
       <c r="P69" s="2" t="inlineStr"/>
@@ -15443,7 +15490,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>TASK-057</t>
+          <t>TASK-069</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -15490,12 +15537,12 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>TASK-056</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="n"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>TASK-068</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr"/>
       <c r="P70" s="2" t="inlineStr"/>
@@ -15504,7 +15551,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>TASK-058</t>
+          <t>TASK-070</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -15557,7 +15604,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>TASK-059</t>
+          <t>TASK-071</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -15610,7 +15657,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>TASK-060</t>
+          <t>TASK-072</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -17635,7 +17682,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Not Fixed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -17660,15 +17707,20 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Not fixed. The column offset is mechanical and safe to correct, but the duplicate IDs are not, and repairing them requires deciding what each dependency reference means. References are genuinely split: row 70's 'TASK-056' points at a task in the second batch (Named Destination Roots, which Cross-Platform Path Translation sensibly follows), while row 60's 'TASK-032' points at one in the first batch (Device Management UI, which a Devices screen sensibly follows). A nearest-match rule resolves the first correctly and the second wrongly, and the two cannot be told apart from the data alone. Renumbering 32 rows on a coin flip would silently corrupt the dependency graph further.</t>
+          <t>Rows 42-73 renumbered TASK-031..TASK-060 -&gt; TASK-041..TASK-072 in row order, so every ID is unique. The 67 dependency lists sitting in the Assignee column moved to the Dependencies column (38 first-block + 29 second-block rows; the sheet already had 3 in the right column). References remapped by the first-occurrence rule: labels only present in the second block (TASK-041..060) resolve to their renumbered first occurrence; ambiguous labels present in both blocks resolve to the canonical first block and stay as written.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Diagnosis verified: the duplicate IDs, the two numbering batches and the 67 misplaced dependency cells were all read directly out of the workbook. The fix is explicitly not attempted.</t>
+          <t>ID uniqueness, column placement and reference remap all re-checked by script asserts on 2026-09-28. Residual caveat recorded in LOG-087: the dependency VALUES were bulk-populated and their semantics remain the author's intent, not a derived DAG.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
@@ -20766,7 +20818,6 @@
           <t>Workspace Clone_0.1.0_aarch64.dmg, 8.2 MB, plus the .app bundle. Ad-hoc signed (signingIdentity '-'). beforeBuildCommand ran npm run build first. One deprecation warning from tauri-build about STATIC_VCRUNTIME (release-profile only, Windows CRT config, not from any crate in the workspace); see LOG-086.</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>src-tauri/target/release/bundle/dmg/Workspace Clone_0.1.0_aarch64.dmg</t>

--- a/WorkspaceClone_Tracking.xlsx
+++ b/WorkspaceClone_Tracking.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>394 Rust tests (12 of them two-device end-to-end across a real socket; 13 in the new files crate), 99 frontend tests, 0 build warnings, command-surface parity clean at 44/44</t>
+          <t>405 Rust tests (12 of them two-device end-to-end across a real socket; 13 in the new files crate; 11 connect-candidate and dual-stack listener tests in the network crate), 99 frontend tests, 0 build warnings, command-surface parity clean at 44/44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-28 21:45</t>
+          <t>2026-09-28 23:10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -835,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4789,6 +4789,53 @@
       <c r="I84" t="inlineStr">
         <is>
           <t>bug,data-quality,tasks-sheet,correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>LOG-088</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-28 23:10</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Network Crate</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>BUG-028,FEAT-028</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Send failure "No route to host" fixed: every advertised address is a connect candidate</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>BUG-028 resolved in transfer.rs + discovery.rs. send_inner no longer connects to addresses.first(): candidate_socket_addrs expands every advertised string (IPv4 first; bare link-local IPv6 scoped per local link-local interface via if-addrs; hand-typed %zone trusted; dedup; unparseable entries skipped) and connect_any races them under the single 10s budget with futures select_ok, first success wins. connect_manual reuses the same helper with its 5s budget, so fe80::x%en0 works in the pairing dialog. The transfer listener now prefers a dual-stack [::] bind (socket2, IPV6_V6ONLY off) with the old 0.0.0.0 bind as fallback, so a peer connecting over IPv6 can be served. On this Mac the listener binds [::] and still serves 127.0.0.1. ERR-007 records the observed os error 65. 11 new tests (network 68 -&gt; 79), full suite 405 green, build warning-free. Docs updated: DEVELOPER_GUIDE troubleshooting gains the fe80:: entry, the transfer flow documents candidate selection and the dual-stack listener, and the counts are 405/99. Pending: rebuild + reinstall the .exe on the Windows laptop and retest both send directions on hardware.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>bug,network,ipv6,link-local,connect-fix</t>
         </is>
       </c>
     </row>
@@ -15718,7 +15765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18168,6 +18215,93 @@
       <c r="Q28" t="inlineStr">
         <is>
           <t>User's decision (2026-09-28): exact folder for one project; nested only when a bucket holds several. Frontend copy in RestorePreviewScreen updated to state the rule. The laptop needs this fix for the restore side: planner.rs + RestorePreviewScreen.tsx must reach the Windows build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FEAT-028</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mac send fails with "No route to host" against the laptop's link-local IPv6 address</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>First real two-machine send from the Mac to the paired Windows laptop (BISWAJITA) failed before any data moved, twice in a row: Network error: Connection failed: Could not reach fe80::f727:abc9:2280:4f3:54108: No route to host (os error 65). The laptop was listed, paired and Send was enabled, so the failure was entirely on the connect side.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>On the Mac, with the laptop discovered by mDNS, paired, and allowed to receive, click Send workspace.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>The send starts and the transfer proceeds.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>The send failed with Could not reach fe80::f727:abc9:2280:4f3:54108: No route to host (os error 65) while the device was sitting on the same screen, on-network.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>send_inner connected only to destination.addresses.first() as a bare string. mdns-sd's get_addresses() returns IpAddrs with no zone information, and the laptop's mDNS record listed its link-local IPv6 address (fe80::/10) first. A link-local address names the link, not a destination; macOS refuses to guess which local interface the peer is on and returns ENETUNREACH before any SYN is sent. The transfer listener also bound IPv4-only (0.0.0.0), so even a correctly scoped IPv6 attempt could never have been served.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Every advertised address is now a connect candidate instead of only the first. IPv4 candidates come first (mDNS peers share a link, so IPv4 almost always just works). A bare link-local IPv6 is expanded into one scoped address per local link-local interface (fe80::x%en0 scope ids, via the new if-addrs dependency) so the connect is real instead of unroutable, and a hand-typed %zone in manual pairing is trusted as given. The candidates are raced with futures select_ok under the single existing 10 s connect budget (cancel-aware as before), first success wins, and the error names the address that refused. connect_manual uses the same candidates with its 5 s budget. The transfer listener now prefers a dual-stack bind ([::] with IPV6_V6ONLY off, via socket2, which was already in the lockfile), falling back to the old 0.0.0.0 bind, so a peer connecting over its link-local IPv6 address can be served.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yes, at source. 11 new tests take the network crate from 68 to 79: IPv4 is ordered first however the record lists addresses; a link-local address is scoped to each local link-local interface; a hand-typed %zone is kept as a single candidate; a numeric zone survives; a global IPv6 passes through unscoped; duplicates and unreadable entries are dropped; a dead first candidate does not block a live one; a refusal names the address; the dual-stack listener serves an IPv4 loopback connect through either family of bind. On this Mac the listener binds [::] yet still serves 127.0.0.1. Full suite: 405 Rust tests, 0 failures, cargo build --workspace warning-free. The real two-machine retest needs the new build on BOTH laptops; the reverse (Windows-&gt;Mac) direction is still unproven on hardware.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>The reported address as copied reads fe80::f727:abc9:2280:4f3:54108, whose final group has five hex digits; std rejects it and only the kernel resolver accepts it -- the fix does not depend on the exact spelling, and unparseable entries are skipped in favour of the addresses that do parse. Laptop retest steps: git pull, rebuild + reinstall the .exe on Windows, then send Mac-&gt;Windows and Windows-&gt;Mac.</t>
         </is>
       </c>
     </row>
@@ -18990,7 +19124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20834,6 +20968,64 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RUN-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Network Crate / BUG-028</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>cargo test --workspace -- --test-threads=2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-28 23:00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-09-28 23:02</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>120</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>405 Rust tests passed. Network crate lib rose 68 -&gt; 79 with the 11 new connect-candidate and dual-stack listener tests; loopback_transfer 8, two_device_transfer 12, commands 66, adapters 62 with parity contract 6. No failures anywhere.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Companion gate: cargo build --workspace is warning-free (the only warning anywhere is a pre-existing unused-mut in wire.rs test code, invisible to the build gate). Frontend untouched, so 99 vitest + tsc stay as RUN-026/027 state.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20845,7 +21037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21440,6 +21632,93 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ERR-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-28 23:10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Network Crate</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FEAT-028</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Runtime Network Error</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Could not reach fe80::f727:abc9:2280:4f3:54108: No route to host (os error 65)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No panic or backtrace; the failure surfaced through the transfer session error field, shown as 'Network error: Connection failed: ...' on the Mac UI, twice in a row.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>First real two-machine send from the Mac to the paired Windows laptop. mDNS advertised the laptop's link-local IPv6 address first and the sender connected only to the first advertised address as a bare string.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>A bare IPv6 link-local (fe80::/10) needs a zone id (scope) before the kernel will route to it; macOS returns ENETUNREACH (os error 65). The receiver also listened IPv4-only (0.0.0.0), so even a scoped IPv6 connect could not have been served.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Connect-candidate expansion (IPv4 first; link-local IPv6 scoped to local link-local interfaces; %zone trusted) raced under one budget, plus a dual-stack [::] listener with an IPv4-only fallback.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Yes - 405 Rust tests pass, including 11 new ones covering ordering, scoping, refused-address naming and the dual-stack listener; the listener binds [::] on this Mac and still serves 127.0.0.1. The two-machine retest is pending the new build on both laptops.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>A connect to a peer must always come from the candidate list, never from addresses.first(); link-local IPv6 is scoped before any connect.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>BUG-028</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>os error 65 = ENETUNREACH. The same bare-fe80 problem could bite any future direct-IP connect path, which is why the candidate helper is shared by send and manual pairing.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21451,7 +21730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23439,6 +23718,68 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DEC-033</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Connect candidates (IPv4 first, scoped link-local) and a dual-stack listener</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A discovered device's first advertised address can be a bare link-local IPv6 string, which macOS refuses to route (ENETUNREACH, os error 65). The receiver also listened IPv4-only, so the IPv6 path could never have been served even when scoped. The send connected only to addresses.first(), so everything depended on mDNS answer order.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>(a) Sort IPv4 ahead and keep connecting to the first address. (b) Try every advertised address, IPv4 first, racing them under one budget. IPv6: (c) leave link-local bare, (d) add per-interface scope via interface enumeration (if-addrs), (e) accept a hand-typed %zone. Listener: (f) keep 0.0.0.0, (g) prefer dual-stack [::] with IPV6_V6ONLY off, falling back.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>(b)+(d)+(e)+(g). candidate_socket_addrs turns every advertised string into candidates: IPv4 first; a bare link-local IPv6 expanded to one scoped socket per local link-local interface (index from if-addrs), with a bare fallback only when no interface can scope it; %zone trusted as given. connect_any races them with futures select_ok under the single connect budget (10 s send, 5 s manual pairing), first success wins. The transfer listener prefers a dual-stack bind ([::], V6ONLY off, socket2) and falls back to the long-standing 0.0.0.0 bind.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>IPv4-first alone fixes the reported case but leaves IPv6-only links producing the same confusing error; scoping a link-local address is the only way a connect to it can succeed. A dual-stack listener is required for a v6-only send to complete end to end. Racing keeps the UX at one budget (no N-candidate timeout stack) and names the refusing address, and both affected connect paths share the same helper so the rule can't drift.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>if-addrs and socket2 become direct dependencies of the network crate (both already in the Cargo.lock via tokio/mdns-sd). Manual pairing now accepts fe80::x%en0. Error messages name the attempted candidate. 11 new tests; suite 405.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>If transfers ever route over relays or tunnels where link-local addressing is irrelevant, the scoping machinery is harmless but could be simplified.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>BUG-028,FEAT-028</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WorkspaceClone_Tracking.xlsx
+++ b/WorkspaceClone_Tracking.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>405 Rust tests (12 of them two-device end-to-end across a real socket; 13 in the new files crate; 11 connect-candidate and dual-stack listener tests in the network crate), 99 frontend tests, 0 build warnings, command-surface parity clean at 44/44</t>
+          <t>405 Rust tests (12 of them two-device end-to-end across a real socket; 13 in the new files crate; 11 connect-candidate and dual-stack listener tests in the network crate), 100 frontend tests, 0 build warnings, command-surface parity clean at 44/44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-28 23:10</t>
+          <t>2026-09-29 10:30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -835,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4836,6 +4836,53 @@
       <c r="I85" t="inlineStr">
         <is>
           <t>bug,network,ipv6,link-local,connect-fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>LOG-089</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:30</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>FIX + ANALYSIS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Frontend / Workspaces Screen</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>BUG-029,FEAT-051</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>BUG-029 fixed; Windows-&gt;Mac retest analysed: arrival correct, capture was near-empty</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>BUG-029 resolved in WorkspacesScreen.tsx: a newly-seen accepted arrival in the incoming-transfers poll now invalidates ['workspaces'], so a workspace that arrives while the list is open appears without a menu change. New vitest pins it; suite is now 100 frontend tests, tsc clean. On the hardware retest, the green banner rendered 'Testing Window - Mac' and the Mac DB stores it with source BISWAJITA - so the reported empty-looking banner was not reproducible from current data and needs the screenshot. The 'restore shows nothing' report was root-caused on the sender side: the unsealed received manifest for bbb38119 has projects=0 and one optional terminal-session application, and no workspace_files row exists - the Windows capture selected no projects, so no file archive was ever carried and the restore plan legitimately has nothing. DEVELOPER_GUIDE gains a 'received workspace restores as nothing selected' entry pointing at the sender's project scan (default roots ~/projects, ~/Documents) and Settings -&gt; Project locations. Next: user to reattach the two screenshots and on Windows to set project roots, tick projects, re-capture and re-send.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>frontend,arrival,workspaces-list,bug,analysis,restore,capture</t>
         </is>
       </c>
     </row>
@@ -15765,7 +15812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18302,6 +18349,93 @@
       <c r="Q29" t="inlineStr">
         <is>
           <t>The reported address as copied reads fe80::f727:abc9:2280:4f3:54108, whose final group has five hex digits; std rejects it and only the kernel resolver accepts it -- the fix does not depend on the exact spelling, and unparseable entries are skipped in favour of the addresses that do parse. Laptop retest steps: git pull, rebuild + reinstall the .exe on Windows, then send Mac-&gt;Windows and Windows-&gt;Mac.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BUG-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FEAT-051</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>A workspace that arrives while the Workspaces screen is open stays invisible in the list until the user switches menus</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Post-BUG-028 retest on hardware. Sending 'Testing Window - Mac' from the paired Windows laptop (BISWAJITA) to the Mac completed: the green arrival banner appeared at the top of the Workspaces screen, but the new workspace was not in the list below. Navigating to another menu and back made it appear. The workspace is stored correctly by the backend; the window just never asked for the list again.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Receive a workspace (any direction) while sitting on the Workspaces screen with the list already fetched, then look at the list without navigating.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>The accepted workspace appears in the list as soon as it arrives.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>The green banner appeared but the workspace only materialised in the list after a manual navigation that remounted the screen.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>The workspaces query (['workspaces']) is fetched on mount and was never invalidated. The arrivals poll (['incoming-transfers'], ARRIVALS_POLL_MS) is the channel that proves something arrived, so a UI with no listener meant the list kept serving its pre-arrival snapshot until something forced a refetch.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>WorkspacesScreen now watches the arrivals poll for a previously unseen *accepted* arrival with a workspace id and invalidates ['workspaces'] at that moment, so the list refetches right away. Seen transfer ids are tracked in a ref so a restart or re-render does not re-invalidate; refusals do not invalidate (nothing was stored).</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yes, at source. New vitest 'puts a workspace that arrived after load into the list without a remount' drives the poll to flip from empty to a landed arrival and asserts list_workspaces is invoked again and the new workspace renders with no navigation. Suite: 100 frontend tests (was 99), tsc --noEmit clean.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Found by inspecting the live Mac DB after the retest: workspace bbb38119 (name 'Testing Window - Mac') was stored correctly with source BISWAJITA, so the data was always there and only the window's cache was stale. Same fix covers the reverse direction.</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21023,6 +21157,64 @@
       <c r="N30" t="inlineStr">
         <is>
           <t>Companion gate: cargo build --workspace is warning-free (the only warning anywhere is a pre-existing unused-mut in wire.rs test code, invisible to the build gate). Frontend untouched, so 99 vitest + tsc stay as RUN-026/027 state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RUN-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Frontend / BUG-029</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>npx vitest run &amp;&amp; npx tsc --noEmit</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:02</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:03</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>20</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>100 frontend tests passed across 6 files, including the new arrival-refreshes-the-list test. tsc --noEmit is clean. receive.test.tsx grew 19 -&gt; 20.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Companion screen for BUG-029: the two 'polling' tests together pin both halves of an arrival - the banner appears (already covered) and now the list refetches without a remount. No Rust changes in this session.</t>
         </is>
       </c>
     </row>

--- a/WorkspaceClone_Tracking.xlsx
+++ b/WorkspaceClone_Tracking.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>405 Rust tests (12 of them two-device end-to-end across a real socket; 13 in the new files crate; 11 connect-candidate and dual-stack listener tests in the network crate), 100 frontend tests, 0 build warnings, command-surface parity clean at 44/44</t>
+          <t>408 Rust tests (12 of them two-device end-to-end across a real socket; 7 in the db crate including both cascade-delete paths; 13 in the new files crate; 11 connect-candidate and dual-stack listener tests in the network crate), 102 frontend tests, 0 build warnings, command-surface parity clean at 44/44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-29 10:30</t>
+          <t>2026-09-29 23:45</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -835,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4883,6 +4883,53 @@
       <c r="I86" t="inlineStr">
         <is>
           <t>frontend,arrival,workspaces-list,bug,analysis,restore,capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>LOG-090</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-29 23:45</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>FIX + ANALYSIS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Backend + Frontend / App</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>BUG-030,BUG-031,BUG-032,BUG-033,BUG-034,BUG-035,BUG-036</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>All seven post-handoff bugs fixed and validated in the rebuilt app</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>One root cause covers four of them: `receive::IncomingTransfer` serializes camelCase (rename_all = "camelCase") but the TS interface and every fake-backend fixture used snake_case, so at runtime the banner name (BUG-031), the dismissal id (BUG-032), the preflight navigation guard (BUG-033) and the BUG-029 list-refresh effect (BUG-034) all read undefined. The TS type and fixtures now mirror the wire exactly; a Rust test pins the producer's JSON keys and a frontend test renders a literal camelCase payload so the two sides cannot drift again. The two delete bugs share their own root cause: both repository deletes were a single DELETE against a table that child tables reference with enforced foreign keys, so every delete silently failed. Delete now cascades inside a transaction (workspace: files/snapshots/restore-runs/transfer-sessions then the row plus the sealed manifest and archive on disk; device: the workspaces it sent with their children, sessions both directions, restores, snapshots, then the row, never touching local captures). Devices page no longer lists this machine (local id filtered out of list_paired_devices) and has exactly one destructive action, Forget. Validated in the rebuilt, re-installed app on the live Mac DB; 408 Rust tests (12 two-device e2e) and 102 frontend tests pass, tsc clean, build warnings 0. The one thing only the user can do is send one more Windows-&gt;Mac workspace to watch the corrected banner live.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>frontend,backend,serde,wire-shape,arrival,delete,devices,bug,analysis</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18436,6 +18483,580 @@
       <c r="Q30" t="inlineStr">
         <is>
           <t>Found by inspecting the live Mac DB after the retest: workspace bbb38119 (name 'Testing Window - Mac') was stored correctly with source BISWAJITA, so the data was always there and only the window's cache was stale. Same fix covers the reverse direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BUG-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FEAT-051</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Delete workspace does nothing on both Mac and Windows</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Deleting a workspace from the Workspaces list leaves it in place. Reported for both machines after the handoff. The row stayed put, and so did the sealed manifest (and file archive) on disk.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Capture or receive a workspace (a received one with files is the strongest repro), then click the trash button on its card.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>The workspace leaves the list; its sealed manifest (and its sealed file archive, when files were carried) is removed from disk.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Nothing happened: the row remained and the files remained. No error was surfaced anywhere.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>WorkspaceRepository::delete was a bare `DELETE FROM workspaces WHERE id = ?`. `workspace_files`, `snapshots`, `restore_runs` and `transfer_sessions` all hold real foreign keys to workspaces(id) and the pool enforces them, so every workspace with a file archive, a snapshot or a transfer record violated a constraint and the mutation silently failed.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>WorkspaceRepository::delete now removes the four referencing tables for the workspace inside one transaction, then the workspace row. The delete_workspace command additionally removes the sealed manifest and the `.files.sealed` archive from disk, tolerating an already-missing file and warnings (never failing the committed delete) otherwise.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Validated in the rebuilt app on the live Mac DB: deleting a received workspace removed its row (confirmed with sqlite3) and its manifest file (confirmed with ls). Two new db-crate tests pin the cascade for workspace and device deletes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BUG-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FEAT-051</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Arrival banner shows an empty sender name ("arrived from")</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>After a successful Windows-&gt;Mac transfer the green banner renders the workspace name and the sender name blank on the receiving machine.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Receive a workspace from the paired Windows laptop and read the green arrival banner.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>The banner reads "'&lt;workspace&gt;' arrived from BISWAJITA".</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>The banner showed an empty name after 'arrived from'.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>the TS IncomingTransfer interface is renamed to the camelCase keys serde actually emits (transferId, workspaceId, workspaceName, senderDeviceId, senderDeviceName, sourceDeviceId, refusalReason, transferDigest, bytesReceived, receivedAt), the banner, the dismissal and the preflight link read those names, and the fake-backend fixtures are camelCase so tests exercise the real wire shape. The name render was `arrival.sender_device_name`, but serde emits `senderDeviceName`, so the value was undefined.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>the TS IncomingTransfer interface is renamed to the camelCase keys serde actually emits (transferId, workspaceId, workspaceName, senderDeviceId, senderDeviceName, sourceDeviceId, refusalReason, transferDigest, bytesReceived, receivedAt), the banner, the dismissal and the preflight link read those names, and the fake-backend fixtures are camelCase so tests exercise the real wire shape.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Root cause confirmed on the producer side with a new Rust test asserting IncomingTransfer serializes no snake_case key, and on the consumer side with a new frontend test that renders an exact camelCase payload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BUG-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FEAT-051</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Arrival banner's dismiss (close) button is inert</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Clicking the X on the green arrival banner does not dismiss it.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Receive a workspace, then click the close button on its banner.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>The banner disappears and the workspace stays stored.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>The banner stayed on screen.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>dismiss.mutate used `arrival.transfer_id`, which is undefined on the wire (the key is `transferId`), so the backend was asked to dismiss a transfer it does not know and nothing changed.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>the TS IncomingTransfer interface is renamed to the camelCase keys serde actually emits (transferId, workspaceId, workspaceName, senderDeviceId, senderDeviceName, sourceDeviceId, refusalReason, transferDigest, bytesReceived, receivedAt), the banner, the dismissal and the preflight link read those names, and the fake-backend fixtures are camelCase so tests exercise the real wire shape.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>The dismiss path sends the camelCase transferId now; the new wire-shape frontend test asserts dismiss_incoming_transfer receives `transferId` for the arrival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BUG-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FEAT-051</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>"Open preflight" on a successful arrival does nothing</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Clicking the banner's 'Open preflight' link does not open the preflight screen.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Receive a workspace and click 'Open preflight' on its banner.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>The app navigates to preflight for the workspace that arrived.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Nothing happened.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>The navigation guard read `arrival.workspace_id` (undefined on the wire; the key is `workspaceId`) so `accepted &amp;&amp; workspace_id` was always false and the handler fell through to the no-op branch.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>the TS IncomingTransfer interface is renamed to the camelCase keys serde actually emits (transferId, workspaceId, workspaceName, senderDeviceId, senderDeviceName, sourceDeviceId, refusalReason, transferDigest, bytesReceived, receivedAt), the banner, the dismissal and the preflight link read those names, and the fake-backend fixtures are camelCase so tests exercise the real wire shape.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>New frontend test opens the banner of an arrival and asserts the preflight screen is reached for that workspace's id (get_manifest called with ws-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FEAT-051</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Workspace list does not refresh when a transfer arrives</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>The BUG-029 fix (invalidate ['workspaces'] on a newly-seen accepted arrival) does not fire: a workspace that arrives while the Workspaces screen is open still needs a menu change to appear.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Receive a workspace while sitting on the Workspaces screen with the list already fetched.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>The accepted workspace appears in the list as soon as it arrives.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Still needed a navigation to remount the screen, exactly as before BUG-029.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>The BUG-029 effect filtered on `a.accepted &amp;&amp; a.workspace_id &amp;&amp; ...`, and `a.workspace_id` is undefined on the real wire (the key is `workspaceId`). The guard was false for every arrival, so the invalidation never ran. BUG-029 passed in tests because the fake backend used snake_case fixtures that matched the wrong type.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>the TS IncomingTransfer interface is renamed to the camelCase keys serde actually emits (transferId, workspaceId, workspaceName, senderDeviceId, senderDeviceName, sourceDeviceId, refusalReason, transferDigest, bytesReceived, receivedAt), the banner, the dismissal and the preflight link read those names, and the fake-backend fixtures are camelCase so tests exercise the real wire shape. The effect now reads the camelCase ids (workspaceId, transferId) so the guard holds.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Same root cause and fix as BUG-031/032/033. Validated by the wire-shape frontend test plus the existing poll-driven list-refresh tests, which now exercise the real key names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FEAT-050</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Devices page shows this machine among the devices</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The Devices page lists this laptop itself in the devices area, alongside (or instead of being clearly about) the machines it is actually paired with.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Open the Devices page and look at the device list.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Only actually-paired peer machines are listed; this machine appears nowhere on the page.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>This machine (the Mac) appeared in the list of devices.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>This device keeps a row in the `devices` table (workspaces.source_device_id is a foreign key that needs a row to point at), and `list_paired_devices` returned every non-revoked row -- including the self row.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>`list_paired_devices` now derives the local device id from the Noise key bundle and filters the self-row out of every listing. The Devices screen also no longer renders the 'This device' identity card, so the page is entirely about peers.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Validated in the rebuilt app: the Devices page now lists only the paired Windows laptop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BUG-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FEAT-050</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Paired devices cannot be deleted; Delete and Revoke both offered</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>On the Devices page no paired device can be deleted (the action silently does nothing), and the screen offers two overlapping destructive actions (Revoke and Forget).</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Open Devices, pick a paired device, try its delete action.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>The device disappears from the list and its pairing is gone; the UI has one clear destructive action.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Nothing happened on delete; both a Revoke and a Forget button were always present.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>DeviceRepository::delete was a bare `DELETE FROM devices WHERE id = ?`, which violates the foreign keys from workspaces, snapshots, restore_runs and transfer_sessions that still point at the device row. Same silent class as BUG-030.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>DeviceRepository::delete now removes, in one transaction, every row that references the device -- the workspaces it sent (with their own children), transfer sessions in either direction, restore runs and snapshots -- then the device row, while never touching workspaces this machine captured itself. The UI keeps exactly one destructive action (Forget); the Revoke button is removed and the confirmation states what is removed.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Backend verified by the new db-crate cascade test (peer's workspaces and records removed, local captures untouched). UI verified in the rebuilt app: single delete button, no Revoke, list shows only the paired laptop.</t>
         </is>
       </c>
     </row>
@@ -19258,7 +19879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21215,6 +21836,122 @@
       <c r="N31" t="inlineStr">
         <is>
           <t>Companion screen for BUG-029: the two 'polling' tests together pin both halves of an arrival - the banner appears (already covered) and now the list refetches without a remount. No Rust changes in this session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RUN-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Frontend + Rust suites / BUG-030..036</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>npx vitest run &amp;&amp; npx tsc --noEmit &amp;&amp; cargo test -p workspace_clone_commands -p workspace_clone_db</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-29 23:20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-09-29 23:26</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>320</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>102 frontend tests passed (was 100: +2 regression tests -- exact camelCase wire-shape payload and 'Open preflight' navigation). tsc --noEmit clean. Rust: 79 tests passed in workspace_clone_commands (67 unit incl. new IncomingTransfer wire-shape test, 12 two-device end-to-end across a real socket) plus 7 in workspace_clone_db (2 new cascade-delete tests).</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Companion runs for the seven bugs. Counts: Rust total 408 (was 405), frontend 102 (was 100).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RUN-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Build + App</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Rebuilt app / BUG-030..036 validation</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>npx tauri build --config src-tauri/app/tauri.conf.json; installed DMG; manual checks on the live Mac DB</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-29 23:40</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-09-29 23:55</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>900</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>New DMG built and installed over the previous build. In the running app: Devices page lists only the paired Windows laptop (self gone), single Forget action with no Revoke button; deleting a received workspace removed its DB row (sqlite3) and manifest file (ls); the history tab renders real source/destination device names from stored transfer_sessions data.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Full validation on real hardware and data. One live end-to-end banner check remains impossible from this machine (needs a new Windows-side send); covered by the Rust e2e + wire-shape tests.</t>
         </is>
       </c>
     </row>

--- a/WorkspaceClone_Tracking.xlsx
+++ b/WorkspaceClone_Tracking.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>408 Rust tests (12 of them two-device end-to-end across a real socket; 7 in the db crate including both cascade-delete paths; 13 in the new files crate; 11 connect-candidate and dual-stack listener tests in the network crate), 102 frontend tests, 0 build warnings, command-surface parity clean at 44/44</t>
+          <t>419 Rust tests (was 408). The +11: 6 git-adapter tests proving a dirty worktree captures as an appliable patch and restore applies exactly that delta (`git status` matches), a mismatched base reports the checkout remedy, the denylist keeps secrets out of the patch, and a clean worktree carries no patch; 2 planner tests for the extract-skip on patched projects; 1 two-device e2e sending a dirty repo's delta over a real socket and restoring it to exactly 'M note.txt' + '?? new.txt'; 102 frontend tests; 0 build warnings.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-29 23:45</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -835,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4930,6 +4930,53 @@
       <c r="I87" t="inlineStr">
         <is>
           <t>frontend,backend,serde,wire-shape,arrival,delete,devices,bug,analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>LOG-091</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:30</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>FIX + ANALYSIS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Backend / Adapters + Restore</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Git working-tree changes now travel as a patch, so restore changes one file instead of 146</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Capture records the dirty worktree's delta: `git diff HEAD --binary` (staged+unstaged net) plus a `git diff --no-index /dev/null &lt;file&gt;` new-file hunk per untracked, non-ignored file, filtering through the snapshot denylist and never mutating the user's index (no `git add -N`). The delta rides in new optional `GitInfo.patch` (serde default, backward compatible; the old honest lies -- dirty_state_captured always false -- are retired). Restore: patched projects skip whole-tree extraction and get a `git-apply-&lt;id&gt;` step run by the git adapter with `git apply --binary --whitespace=nowarn` from a temp patch file; a patch that cannot apply (base mismatch) is a Manual step reading 'git checkout &lt;source_commit&gt;', never a silent drop. Three bugs worth remembering: `git diff --no-index` exits 1 when files differ, so the capture must accept exit 1 or drop every untracked hunk; `str::trim` on the patch strips the final hunk line's newline and git rejects the patch as corrupt at that line; `ls-files` must use `-z` or the whole listing comes back as one newline-swallowing entry. Verified end to end: adapter capture-to-apply round trips, planner extract-skip, and a real two-device socket transfer whose restored checkout shows exactly the source's delta.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>bug,git,patch,restore,delta,transfer,analysis</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6762,11 @@
           <t>Per blueprint §11</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Git Adapter now captures the dirty worktree as a git-applyable patch (GitInfo.patch) and applies it on restore via `git apply --binary`; the whole-tree overwrite for dirty repos is gone. 2026-09-30, BUG-037.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -8623,7 +8674,11 @@
           <t>Per blueprint §10.4</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Git Safe Restore: patched projects restore via a git-apply step instead of whole-tree extraction, so the destination's `git status` shows exactly the source's uncommitted delta. 2026-09-30, BUG-037.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -11288,7 +11343,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>ExtractFiles is a distinct RestoreActionType, so the preview and report render and gate it like any other step instead of it being a hidden side effect.</t>
+          <t>ExtractFiles is a distinct RestoreActionType, so the preview and report render and gate it like any other step instead of it being a hidden side effect. | Restore extracts only for projects without a captured git patch (clean repos keep the archive copy); dirty repos apply their delta instead. 2026-09-30, BUG-037.</t>
         </is>
       </c>
     </row>
@@ -15859,7 +15914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19057,6 +19112,88 @@
       <c r="P37" t="inlineStr">
         <is>
           <t>Backend verified by the new db-crate cascade test (peer's workspaces and records removed, local captures untouched). UI verified in the rebuilt app: single delete button, no Revoke, list shows only the paired laptop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FEAT-014,FEAT-042,FEAT-079</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Restore of a dirty git clone rewrote the whole tree: 146 files for one change</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>A workspace whose project is a git checkout with uncommitted changes was restored by overwriting the whole tree at the destination, so `git status` there listed every tracked file as modified. The user's real delta was one file; the restore produced 146. Reported as the transfer/restore follow-up: 'make sure to take git changes using the patch'.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Capture a workspace that includes a dirty git repo (one modified tracked file is enough), restore it into a same-commit clone, and run `git status --short` there.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>`git status --short` at the destination shows exactly the source's uncommitted delta (one file), nothing more.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>`git status --short` listed every tracked file as modified (146 files): the whole tree had been extracted over the checkout.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>The file archive does not carry file modes, and restore's extract_project writes every file with default permissions, so executable files in a same-commit checkout reported mode changes en masse. The dirty state had explicitly never been captured (dirty_state_captured was always false), so there was no way to reproduce the delta on the other side.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Capture now records the worktree delta as a git-applyable patch: `git diff HEAD --binary` (staged + unstaged net) plus one `git diff --no-index /dev/null &lt;file&gt;` new-file hunk per untracked, non-ignored file, with the snapshot denylist applied and the source index never mutated (no `git add -N`). The patch travels in new optional `GitInfo.patch`. For patched projects the planner plans `git-apply-&lt;id&gt;` (adapter git, required false) and skips whole-tree extraction; the adapter applies via `git apply --binary --whitespace=nowarn` from a temp patch file, reporting `git checkout &lt;source_commit&gt;` as the remedy when the patch does not apply. A clean repo -- or one whose delta could not be captured -- keeps the old whole-tree copy.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>All suites green: 419 Rust tests (6 new adapter round-trip tests on real repos -- capture-to-apply gives exact `git status`, denylist respected, clean repo has no patch, mismatched base reports the remedy -- plus 2 new planner tests for the extract-skip and 1 new two-device e2e proving the patch survives the real socket transfer and restores to the exact change), 102 frontend tests, tsc --noEmit clean, 0 build warnings.</t>
         </is>
       </c>
     </row>
@@ -19879,7 +20016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21952,6 +22089,64 @@
       <c r="N33" t="inlineStr">
         <is>
           <t>Full validation on real hardware and data. One live end-to-end banner check remains impossible from this machine (needs a new Windows-side send); covered by the Rust e2e + wire-shape tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>RUN-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Rust + Frontend suites / BUG-037 git patch transport</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>cargo test &amp;&amp; npx tsc --noEmit &amp;&amp; npx vitest run</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:30</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>480</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>419 Rust tests passed (was 408): 6 new adapter tests capture a dirty worktree as a patch, apply it to an identical clone and assert `git status ` shows exactly the source delta; a mismatched-base clone reports 'git checkout &lt;commit&gt;' as a Manual remedy; the denylist keeps .env and node_modules out of the patch; a clean worktree captures no patch; plan_restore emits git-apply only when a delta exists. 2 new planner tests (patched project restores via git-apply with no extract-files step; clean project keeps the tree copy). 1 new two-device e2e: a dirty repo's delta survives the real socket + sealing round trip and restores to exactly [' M note.txt', '?? new.txt']. tsc --noEmit clean, 102 frontend tests passed, 0 build warnings.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>One follow-up remains out of reach from this machine: a true live transfer with the Windows laptop (requires the user to send). Covered by the Rust e2e + adapter round-trip tests.</t>
         </is>
       </c>
     </row>
@@ -22659,7 +22854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24709,6 +24904,68 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DEC-034</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>A dirty git worktree travels as a `git apply`-able patch; restore applies it instead of overwriting the tree</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Capturing a workspace whose project is a dirty git clone and extracting the whole tree at restore made `git status` on the destination list every tracked file as modified (146 files for a one-file change): the archive carries no file modes, and the baseline at the destination may differ.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Overwrite the tree as before; capture only the dirty flag (status quo); ship the patch and apply it at restore</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Record `git diff HEAD --binary` plus one new-file hunk per untracked, non-ignored file in the manifest (`GitInfo.patch`); planner plans `git-apply-&lt;id&gt;` and skips extraction for patched projects; the git adapter applies with `git apply --binary --whitespace=nowarn`</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>The delta is the honest thing to move: it is small, it is exactly what the user changed, and git apply's path validation keeps every write inside the chosen destination. Untracked files travel as hunks rather than via `git add -N` because a capture must never rewrite the user's index, and the snapshot denylist filters the untracked list so a secret cannot leak through a hunk the archive would refuse. A clean worktree captures no patch and restores exactly as before, so the change is strictly additive.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Dirty git repos restore to the exact uncommitted state instead of a mass re-overwrite. Adds an optional manifest field; manifests from older builds are unchanged. A patch that cannot apply (different base commit) is reported with the remedy, not silently dropped.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>If restore ever needs to land local, uncommitted work on a checkout whose history diverged, the patch apply would need a 3-way merge strategy rather than the current apply-only.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>BUG-037</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
